--- a/input_data/complex_formation.xlsx
+++ b/input_data/complex_formation.xlsx
@@ -13,8 +13,6 @@
     <sheet name="Sole YidC IMP" sheetId="3" state="visible" r:id="rId4"/>
     <sheet name="Peri MP in Cyto" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="Predefined Complexes" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="ATPSynthase" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="ABC Transporter OLD" sheetId="7" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="166">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -205,7 +203,7 @@
     <t xml:space="preserve">ABCTransporter</t>
   </si>
   <si>
-    <t xml:space="preserve">NBD 0425</t>
+    <t xml:space="preserve">NBD 0427</t>
   </si>
   <si>
     <t xml:space="preserve">thmppABC</t>
@@ -304,7 +302,7 @@
     <t xml:space="preserve">1;3;1;3;1;2;10;1</t>
   </si>
   <si>
-    <t xml:space="preserve">epsilon</t>
+    <t xml:space="preserve">epsilon 0789</t>
   </si>
   <si>
     <t xml:space="preserve">SMC</t>
@@ -524,63 +522,6 @@
   </si>
   <si>
     <t xml:space="preserve">RNAP_core</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gene</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stoi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subunit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNaseY_Dimer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0359;0359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0359/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNaseJ1J2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0600;0257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">min(0600, 0257)</t>
   </si>
 </sst>
 </file>
@@ -1870,448 +1811,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.9453125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="1" width="8.94"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultColWidth="8.9453125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="3" style="1" width="8.94"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>103</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>120</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>